--- a/Timeliste - Juli.xlsx
+++ b/Timeliste - Juli.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erlen\Documents\Github\Crystallographic-Reality\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72214B6C-3C35-4F8C-8394-B6848FFB2756}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB9C206-DE19-4C94-9342-B7736DFBB38E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{36930395-203A-46D0-A2AB-0BDFDA6E0730}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>NAVN</t>
   </si>
@@ -93,9 +93,6 @@
   </si>
   <si>
     <t>Juli</t>
-  </si>
-  <si>
-    <t>start 10 min earlier</t>
   </si>
 </sst>
 </file>
@@ -1218,9 +1215,7 @@
     </row>
     <row r="25" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
-      <c r="B25" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="7" t="str">
         <f t="shared" si="0"/>
